--- a/dev-docs/rule-0724-组件模板配置/组件模板.xlsx
+++ b/dev-docs/rule-0724-组件模板配置/组件模板.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-填写说明" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,54 +13,84 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="加工费" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="002F5496"/>
+      <color rgb="FF2F5496"/>
       <sz val="15"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="FFC00000"/>
       <sz val="12"/>
     </font>
     <font>
-      <color rgb="00808080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF808080"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00BF8F00"/>
+      <color rgb="FFBF8F00"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="002F5496"/>
+      <color rgb="FF2F5496"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -70,26 +99,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
+        <fgColor rgb="FF2F5496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -99,23 +133,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -123,32 +182,19 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,10 +207,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -177,9 +219,20 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -542,21 +595,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>组件模板配置表（极简）</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>你只填 2 项</t>
@@ -571,11 +624,11 @@
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>其余（字段类型 / 别名 / 绑定路径 / SQL视图 / 标准字段的数据来源）我按 rule-0724 规则自动推导，不用你填。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>其余（字段类型 / 别名 / 绑定路径 / SQL视图 / 数据来源）我按 rule-0724 规则自动推导。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>可选（想更准就填）</t>
@@ -583,11 +636,11 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>③ 勾选每字段的角色：料号列 / 名称列 / 行键 / 排序列（灰色列，留空我按规则推荐）  ④ 非标准字段的【数据来源】（标准字段留空即可）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>③ 勾选每字段角色：料号列/名称列/行键/排序列/接价格策略（灰绿列，留空我按规则推荐）  ④ 备注：想特别交代就用大白话写</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>页签类型 tabType</t>
@@ -667,10 +720,10 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>角色标注（可选）</t>
+          <t>角色标注（可选，打✓）</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -683,7 +736,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>该页签的料号是哪个字段（材质元素/零件/外购件/主件 各一个）</t>
+          <t>该页签的料号是哪个字段。你的模板没有料号列 → 留空即可：我不会凭空加列，料号只在取数 SQL 里做关联键用</t>
         </is>
       </c>
     </row>
@@ -695,7 +748,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>料号名称字段（可选）</t>
+          <t>料号名称字段（没有料号列时靠它认行，建议标上；料号列/名称列至少要有一个）</t>
         </is>
       </c>
     </row>
@@ -707,7 +760,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>进行唯一键的字段（多行组件；一号多材质须含材质料号）</t>
+          <t>进行唯一键的字段（多行组件必标；同一料号有多种材质时，「材质」必须进行键）</t>
         </is>
       </c>
     </row>
@@ -719,14 +772,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>按它数字正序的字段（项次/序号，标一个）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>※ 颜色：黄色=需你填；灰色=可选/我推导。详细配置规则见同目录 1~5 / 报价侧 / 核价侧 .md。</t>
+          <t>按它数字正序（项次/序号，标一个）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>接价格策略</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>⭐该字段（元素单价/货币）从【客户价格策略】自动带，不手填——在该字段打✓即声明</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>※ 颜色：黄=需你填；灰=可选/我推导；绿=接价格策略勾选。详细规则见同目录 1~5 / 报价侧 / 核价侧 .md。</t>
         </is>
       </c>
     </row>
@@ -741,15 +806,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="2" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,150 +821,159 @@
           <t>页签类型 tabType</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>主件</t>
         </is>
       </c>
-      <c r="C1" s="11" t="n"/>
+      <c r="C1" s="17" t="n"/>
+      <c r="D1" s="18" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>字段名</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>料号列</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>名称列</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>行键</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>排序列</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>数据来源(选填,标准字段留空)</t>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>接价格策略</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>备注(选填,大白话)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>销售料号</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>客户料号名称</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>客户产品编号</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>报价货币</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>报价</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>手填,无源</t>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>销售手填，不带数据</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"主件,材质元素,零件,外购件,BOM,(空)"</formula1>
     </dataValidation>
-    <dataValidation sqref="B4:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓"</formula1>
     </dataValidation>
   </dataValidations>
@@ -915,15 +987,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="2" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -932,218 +1002,235 @@
           <t>页签类型 tabType</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>材质元素</t>
         </is>
       </c>
-      <c r="C1" s="11" t="n"/>
+      <c r="C1" s="17" t="n"/>
+      <c r="D1" s="18" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>字段名</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>料号列</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>名称列</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>行键</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>排序列</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>数据来源(选填,标准字段留空)</t>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>接价格策略</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>备注(选填,大白话)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>销售料号</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>材质</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>材质料号</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>项次</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>元素</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>组成含量(%)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>损耗率%</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>毛重</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>毛用量单位</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="13" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>元素单价</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>接客户价格策略 f_customer_element_price(单价)</t>
-        </is>
-      </c>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>货币</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>接客户价格策略 f_customer_element_price(货币)</t>
-        </is>
-      </c>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"主件,材质元素,零件,外购件,BOM,(空)"</formula1>
     </dataValidation>
-    <dataValidation sqref="B4:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1157,15 +1244,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="2" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1174,130 +1259,141 @@
           <t>页签类型 tabType</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>外购件</t>
         </is>
       </c>
-      <c r="C1" s="11" t="n"/>
+      <c r="C1" s="17" t="n"/>
+      <c r="D1" s="18" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>字段名</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>料号列</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>名称列</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>行键</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>排序列</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>数据来源(选填,标准字段留空)</t>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>接价格策略</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>备注(选填,大白话)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>销售料号</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>组成件料号</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>组成件名称</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>组成数量</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>组成单位</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"主件,材质元素,零件,外购件,BOM,(空)"</formula1>
     </dataValidation>
-    <dataValidation sqref="B4:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1311,15 +1407,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="2" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1328,150 +1422,158 @@
           <t>页签类型 tabType</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>零件</t>
         </is>
       </c>
-      <c r="C1" s="11" t="n"/>
+      <c r="C1" s="17" t="n"/>
+      <c r="D1" s="18" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>字段名</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>料号列</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>名称列</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>行键</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>排序列</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>数据来源(选填,标准字段留空)</t>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>接价格策略</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>备注(选填,大白话)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>料号</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>unit_price.code(零件料号)</t>
-        </is>
-      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>料件</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>项次</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>工序</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>加工费</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"主件,材质元素,零件,外购件,BOM,(空)"</formula1>
     </dataValidation>
-    <dataValidation sqref="B4:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B4:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓"</formula1>
     </dataValidation>
   </dataValidations>
